--- a/docs/DFW_Rolodex.xlsx
+++ b/docs/DFW_Rolodex.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Permits" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Contacts'!$A$6:$AD$227</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Contacts'!$A$6:$AD$221</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD229"/>
+  <dimension ref="A1:AD223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -593,11 +593,11 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Contacts</t>
+          <t>Rows</t>
         </is>
       </c>
       <c r="B3" s="3">
-        <f>COUNTA($A$7:$A$227)</f>
+        <f>COUNTA($A$7:$A$221)</f>
         <v/>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="D3" s="3">
-        <f>COUNTIF($Q$7:$Q$227,"ok")</f>
+        <f>COUNTIF($Q$7:$Q$221,"ok")</f>
         <v/>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="F3" s="3">
-        <f>COUNTIF($Q$7:$Q$227,"ADD LINKEDIN")</f>
+        <f>COUNTIF($Q$7:$Q$221,"ADD LINKEDIN")</f>
         <v/>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="H3" s="3">
-        <f>SUMPRODUCT((COUNTIF(OFFSET($B$7,ROW($B$7:$B$227)-ROW($B$7),0,1,1),$B$7:$B$227)&gt;0)*($D$7:$D$227="Holds all three counts")/COUNTIF($B$7:$B$227,$B$7:$B$227&amp;""))</f>
+        <f>SUMPRODUCT((COUNTIF(OFFSET($B$7,ROW($B$7:$B$221)-ROW($B$7),0,1,1),$B$7:$B$221)&gt;0)*($D$7:$D$221="Holds all three counts")/COUNTIF($B$7:$B$221,$B$7:$B$221&amp;""))</f>
         <v/>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="J3" s="3">
-        <f>COUNTIF($T$7:$T$227,"YES")</f>
+        <f>COUNTIF($T$7:$T$221,"YES")</f>
         <v/>
       </c>
     </row>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Chief Operating Officer and Executive Vice President, Green Brick Partners</t>
+          <t>President and Chief Operating Officer, Green Brick Partners</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -1662,7 +1662,7 @@
       <c r="T13" s="6" t="inlineStr"/>
       <c r="U13" s="9" t="inlineStr">
         <is>
-          <t>Indexed title reads Jed Dolson - Chief Operating Officer and Executive Vice President - Green Brick Partners, Inc. His LinkedIn title reads COO and EVP of Green Brick Partners, the parent, and he was earlier its Texas Region President over Trophy.</t>
+          <t>Indexed title reads Jed Dolson - Chief Operating Officer and Executive Vice President - Green Brick Partners, Inc. Named on Green Brick's leadership page as President and Chief Operating Officer, previously President of the Texas region over the DFW brands.</t>
         </is>
       </c>
       <c r="V13" s="6" t="inlineStr">
@@ -6536,7 +6536,7 @@
       <c r="T51" s="6" t="inlineStr"/>
       <c r="U51" s="9" t="inlineStr">
         <is>
-          <t>Named in a 2010 Dallas News article as CEO of First Texas, spelled Randall.</t>
+          <t>Named in a 2010 Dallas News article as CEO of First Texas.</t>
         </is>
       </c>
       <c r="V51" s="6" t="inlineStr">
@@ -6912,11 +6912,7 @@
           <t>Builds single-family rental homes for clients under what it calls its BUILD model, as part of the Highland Homes family.</t>
         </is>
       </c>
-      <c r="T54" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="T54" s="12" t="inlineStr"/>
       <c r="U54" s="15" t="inlineStr">
         <is>
           <t>Quoted in a Tricon Residential release as Vice President at HHS Residential.</t>
@@ -7727,7 +7723,7 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Division President, Dallas-Fort Worth, Partners In Building</t>
+          <t>President, Partners In Building, since June 2026. Previously Division President, Dallas-Fort Worth</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
@@ -7806,12 +7802,12 @@
       </c>
       <c r="U61" s="9" t="inlineStr">
         <is>
-          <t>Named in HousingWire, February 24, 2022, as Dallas-Fort Worth Division President of Partners In Building at the Paul Taylor acquisition.</t>
+          <t>Named President in Realty News Report, June 11, 2026, after serving as Division President for DFW.</t>
         </is>
       </c>
       <c r="V61" s="6" t="inlineStr">
         <is>
-          <t>https://www.housingwire.com/articles/a-semi-custom-production-hybrid-fit-for-bumpier-times/</t>
+          <t>https://realtynewsreport.com/houston-home-builder-names-new-leader/</t>
         </is>
       </c>
       <c r="W61" s="6" t="inlineStr">
@@ -7852,7 +7848,7 @@
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>Chief Executive Officer, Partners In Building</t>
+          <t>Chairman, Partners In Building, since June 2026</t>
         </is>
       </c>
       <c r="D62" s="13" t="inlineStr">
@@ -7927,12 +7923,12 @@
       <c r="T62" s="12" t="inlineStr"/>
       <c r="U62" s="15" t="inlineStr">
         <is>
-          <t>Named on the Partners In Building story page as Chief Executive Officer from 2010.</t>
+          <t>Named in Realty News Report, June 2026, as moving from Chief Executive Officer to Chairman.</t>
         </is>
       </c>
       <c r="V62" s="12" t="inlineStr">
         <is>
-          <t>https://partnersinbuilding.com/our-story</t>
+          <t>https://realtynewsreport.com/houston-home-builder-names-new-leader/</t>
         </is>
       </c>
       <c r="W62" s="12" t="inlineStr">
@@ -10158,11 +10154,7 @@
           <t>Makes factory-built wall panels, floor cassettes and roof components as a replacement for stick framing. The plant is in the Houston area, and DFW is inside its shipping radius.</t>
         </is>
       </c>
-      <c r="T80" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="T80" s="12" t="inlineStr"/>
       <c r="U80" s="15" t="inlineStr">
         <is>
           <t>Named General Manager in a February 24, 2022 Community Impact article on the plant opening.</t>
@@ -10397,7 +10389,7 @@
       </c>
       <c r="N82" s="15" t="inlineStr">
         <is>
-          <t>Its core product is offsite wall panels, including StoPanel systems. A panel shop making its normal product reads Partly, as Builders FirstSource's panel plants do.</t>
+          <t>Its core product is offsite wall panels, including StoPanel systems. That changes where the wall is made, not what the wall is.</t>
         </is>
       </c>
       <c r="O82" s="10" t="inlineStr"/>
@@ -10984,7 +10976,7 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>84 Lumber — DFW manufacturing presence</t>
+          <t>84 Lumber, DFW</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr"/>
@@ -11008,7 +11000,7 @@
       </c>
       <c r="H87" s="6" t="inlineStr">
         <is>
-          <t>Dallas door shop, DFW wall-panel plant not confirmed</t>
+          <t>Dallas door shop, no DFW wall-panel plant published</t>
         </is>
       </c>
       <c r="I87" s="8" t="inlineStr">
@@ -11054,7 +11046,7 @@
       </c>
       <c r="S87" s="9" t="inlineStr">
         <is>
-          <t>Supplies components to DFW builders from a national manufacturing line. No wall-panel plant inside the Metroplex is confirmed.</t>
+          <t>Supplies components to DFW builders from a national manufacturing line. No wall-panel plant inside the Metroplex is published.</t>
         </is>
       </c>
       <c r="T87" s="6" t="inlineStr"/>
@@ -11093,7 +11085,7 @@
       </c>
       <c r="B88" s="12" t="inlineStr">
         <is>
-          <t>Builders FirstSource — Fort Worth Truss / Trussway</t>
+          <t>Builders FirstSource, Fort Worth Truss (formerly Trussway)</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr"/>
@@ -11202,7 +11194,7 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>Coreslab Structures (Texas) — DFW territory</t>
+          <t>Coreslab Structures (Texas)</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
@@ -11327,7 +11319,7 @@
       </c>
       <c r="B90" s="12" t="inlineStr">
         <is>
-          <t>Coreslab Structures (Texas) — DFW territory</t>
+          <t>Coreslab Structures (Texas)</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
@@ -11742,7 +11734,7 @@
       </c>
       <c r="L93" s="9" t="inlineStr">
         <is>
-          <t>More than 1,500 staff and millions of square feet a year, per its own site. One or two printers would be a pilot at most.</t>
+          <t>More than 1,500 staff and millions of square feet a year, per its own site.</t>
         </is>
       </c>
       <c r="M93" s="8" t="inlineStr">
@@ -11871,7 +11863,7 @@
       </c>
       <c r="L94" s="15" t="inlineStr">
         <is>
-          <t>More than 1,500 staff and millions of square feet a year, per its own site. One or two printers would be a pilot at most.</t>
+          <t>More than 1,500 staff and millions of square feet a year, per its own site.</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr">
@@ -11952,7 +11944,7 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>UFP Site Built — Hillsboro, TX</t>
+          <t>UFP Site Built, Hillsboro</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
@@ -12077,7 +12069,7 @@
       </c>
       <c r="B96" s="12" t="inlineStr">
         <is>
-          <t>UFP Site Built — Hillsboro, TX</t>
+          <t>UFP Site Built, Hillsboro</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
@@ -12202,7 +12194,7 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>Wells — Hillsboro TX (ex-GATE Precast)</t>
+          <t>Wells, Hillsboro plants</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
@@ -12335,7 +12327,7 @@
       </c>
       <c r="B98" s="12" t="inlineStr">
         <is>
-          <t>Wells — Hillsboro TX (ex-GATE Precast)</t>
+          <t>Wells, Hillsboro plants</t>
         </is>
       </c>
       <c r="C98" s="12" t="inlineStr">
@@ -13185,7 +13177,7 @@
       <c r="T104" s="12" t="inlineStr"/>
       <c r="U104" s="15" t="inlineStr">
         <is>
-          <t>Co-Founder section: David helped start Brick Experts in 2015; master brick mason 30 years prior.</t>
+          <t>Co-Founder section: David helped start Brick Experts in 2015, after 30 years as a master brick mason.</t>
         </is>
       </c>
       <c r="V104" s="12" t="inlineStr">
@@ -15849,7 +15841,7 @@
       </c>
       <c r="N126" s="15" t="inlineStr">
         <is>
-          <t>Large tilt panels, such as the 75-foot panels at Harris Health, are hard work with an existing method, not a new one.</t>
+          <t>Tilt panels, such as the 75-foot panels at Harris Health, use an existing method, not a new one.</t>
         </is>
       </c>
       <c r="O126" s="10" t="inlineStr"/>
@@ -15978,7 +15970,7 @@
       </c>
       <c r="N127" s="9" t="inlineStr">
         <is>
-          <t>Large tilt panels, such as the 75-foot panels at Harris Health, are hard work with an existing method, not a new one.</t>
+          <t>Tilt panels, such as the 75-foot panels at Harris Health, use an existing method, not a new one.</t>
         </is>
       </c>
       <c r="O127" s="10" t="inlineStr"/>
@@ -16107,7 +16099,7 @@
       </c>
       <c r="N128" s="15" t="inlineStr">
         <is>
-          <t>Large tilt panels, such as the 75-foot panels at Harris Health, are hard work with an existing method, not a new one.</t>
+          <t>Tilt panels, such as the 75-foot panels at Harris Health, use an existing method, not a new one.</t>
         </is>
       </c>
       <c r="O128" s="10" t="inlineStr"/>
@@ -16236,7 +16228,7 @@
       </c>
       <c r="N129" s="9" t="inlineStr">
         <is>
-          <t>Large tilt panels, such as the 75-foot panels at Harris Health, are hard work with an existing method, not a new one.</t>
+          <t>Tilt panels, such as the 75-foot panels at Harris Health, use an existing method, not a new one.</t>
         </is>
       </c>
       <c r="O129" s="10" t="inlineStr"/>
@@ -16381,7 +16373,7 @@
       </c>
       <c r="S130" s="15" t="inlineStr">
         <is>
-          <t>Places concrete with boom pumps and placing booms, a trade next to print-crew skills. It does not own walls.</t>
+          <t>Places concrete with boom pumps and placing booms. It does not own walls.</t>
         </is>
       </c>
       <c r="T130" s="12" t="inlineStr">
@@ -16506,7 +16498,7 @@
       </c>
       <c r="S131" s="9" t="inlineStr">
         <is>
-          <t>Places concrete with boom pumps and placing booms, a trade next to print-crew skills. It does not own walls.</t>
+          <t>Places concrete with boom pumps and placing booms. It does not own walls.</t>
         </is>
       </c>
       <c r="T131" s="6" t="inlineStr">
@@ -17077,7 +17069,7 @@
       </c>
       <c r="B136" s="12" t="inlineStr">
         <is>
-          <t>Manhattan Construction Company — Dallas</t>
+          <t>Manhattan Construction Company, Dallas</t>
         </is>
       </c>
       <c r="C136" s="12" t="inlineStr">
@@ -17125,7 +17117,7 @@
       </c>
       <c r="L136" s="15" t="inlineStr">
         <is>
-          <t>The regional arm of a national construction group, so a machine purchase runs through a large desk.</t>
+          <t>The regional arm of a national construction group, so a machine purchase runs through the group.</t>
         </is>
       </c>
       <c r="M136" s="14" t="inlineStr">
@@ -17202,7 +17194,7 @@
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>Manhattan Construction Company — Dallas</t>
+          <t>Manhattan Construction Company, Dallas</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
@@ -17250,7 +17242,7 @@
       </c>
       <c r="L137" s="9" t="inlineStr">
         <is>
-          <t>The regional arm of a national construction group, so a machine purchase runs through a large desk.</t>
+          <t>The regional arm of a national construction group, so a machine purchase runs through the group.</t>
         </is>
       </c>
       <c r="M137" s="8" t="inlineStr">
@@ -17629,7 +17621,7 @@
       </c>
       <c r="L140" s="15" t="inlineStr">
         <is>
-          <t>10,000+ slabs a year on its own site is far beyond what one or two printers would cover. A machine would be a pilot line inside the slab business.</t>
+          <t>10,000+ slabs a year on its own site is far beyond what one or two printers would cover.</t>
         </is>
       </c>
       <c r="M140" s="14" t="inlineStr">
@@ -18742,7 +18734,7 @@
       </c>
       <c r="H149" s="6" t="inlineStr">
         <is>
-          <t>943 closings in 2025 by its DFW division</t>
+          <t>943 Dallas-division closings in 2025, its own press kit</t>
         </is>
       </c>
       <c r="I149" s="8" t="inlineStr">
@@ -18875,7 +18867,7 @@
       </c>
       <c r="H150" s="12" t="inlineStr">
         <is>
-          <t>943 closings in 2025 by its DFW division</t>
+          <t>943 Dallas-division closings in 2025, its own press kit</t>
         </is>
       </c>
       <c r="I150" s="14" t="inlineStr">
@@ -19004,7 +18996,7 @@
       </c>
       <c r="H151" s="6" t="inlineStr">
         <is>
-          <t>943 closings in 2025 by its DFW division</t>
+          <t>943 Dallas-division closings in 2025, its own press kit</t>
         </is>
       </c>
       <c r="I151" s="8" t="inlineStr">
@@ -19137,7 +19129,7 @@
       </c>
       <c r="H152" s="12" t="inlineStr">
         <is>
-          <t>943 closings in 2025 by its DFW division</t>
+          <t>943 Dallas-division closings in 2025, its own press kit</t>
         </is>
       </c>
       <c r="I152" s="14" t="inlineStr">
@@ -22443,11 +22435,7 @@
           <t>Purchasing sits at a national desk.</t>
         </is>
       </c>
-      <c r="T177" s="6" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
+      <c r="T177" s="6" t="inlineStr"/>
       <c r="U177" s="9" t="inlineStr">
         <is>
           <t>Named in Local Profile on June 19, 2025 as Taylor Morrison's Dallas Division President, quoted on Ranch at Uptown Celina.</t>
@@ -23140,7 +23128,7 @@
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t>Cambridge Crossing (Celina — Cambridge Companies)</t>
+          <t>Cambridge Crossing (Celina, Cambridge Companies)</t>
         </is>
       </c>
       <c r="C183" s="6" t="inlineStr">
@@ -23261,7 +23249,7 @@
       </c>
       <c r="B184" s="12" t="inlineStr">
         <is>
-          <t>Cambridge Crossing (Celina — Cambridge Companies)</t>
+          <t>Cambridge Crossing (Celina, Cambridge Companies)</t>
         </is>
       </c>
       <c r="C184" s="12" t="inlineStr">
@@ -23382,7 +23370,7 @@
       </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
-          <t>Cambridge Crossing (Celina — Cambridge Companies)</t>
+          <t>Cambridge Crossing (Celina, Cambridge Companies)</t>
         </is>
       </c>
       <c r="C185" s="6" t="inlineStr">
@@ -24378,7 +24366,7 @@
       </c>
       <c r="B193" s="6" t="inlineStr">
         <is>
-          <t>Light Farms (Republic — Celina)</t>
+          <t>Light Farms (Celina, Republic)</t>
         </is>
       </c>
       <c r="C193" s="6" t="inlineStr">
@@ -24503,7 +24491,7 @@
       </c>
       <c r="B194" s="12" t="inlineStr">
         <is>
-          <t>Light Farms (Republic — Celina)</t>
+          <t>Light Farms (Celina, Republic)</t>
         </is>
       </c>
       <c r="C194" s="12" t="inlineStr">
@@ -24874,7 +24862,7 @@
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t>Mosaic (Celina — Tellus Group)</t>
+          <t>Mosaic (Celina, Tellus Group)</t>
         </is>
       </c>
       <c r="C197" s="6" t="inlineStr">
@@ -25380,7 +25368,7 @@
       </c>
       <c r="J201" s="9" t="inlineStr">
         <is>
-          <t>Large multi-phase masterplans, Walsh and Light Farms, with long buildouts.</t>
+          <t>Multi-phase masterplans, Walsh and Light Farms, with long buildouts.</t>
         </is>
       </c>
       <c r="K201" s="8" t="inlineStr">
@@ -25509,7 +25497,7 @@
       </c>
       <c r="J202" s="15" t="inlineStr">
         <is>
-          <t>Large multi-phase masterplans, Walsh and Light Farms, with long buildouts.</t>
+          <t>Multi-phase masterplans, Walsh and Light Farms, with long buildouts.</t>
         </is>
       </c>
       <c r="K202" s="14" t="inlineStr">
@@ -25634,7 +25622,7 @@
       </c>
       <c r="J203" s="9" t="inlineStr">
         <is>
-          <t>Large multi-phase masterplans, Walsh and Light Farms, with long buildouts.</t>
+          <t>Multi-phase masterplans, Walsh and Light Farms, with long buildouts.</t>
         </is>
       </c>
       <c r="K203" s="8" t="inlineStr">
@@ -25721,7 +25709,7 @@
       </c>
       <c r="B204" s="12" t="inlineStr">
         <is>
-          <t>Serenade (Celina — Huffines Communities)</t>
+          <t>Serenade (Celina, Huffines Communities)</t>
         </is>
       </c>
       <c r="C204" s="12" t="inlineStr">
@@ -25846,7 +25834,7 @@
       </c>
       <c r="B205" s="6" t="inlineStr">
         <is>
-          <t>Serenade (Celina — Huffines Communities)</t>
+          <t>Serenade (Celina, Huffines Communities)</t>
         </is>
       </c>
       <c r="C205" s="6" t="inlineStr">
@@ -25971,7 +25959,7 @@
       </c>
       <c r="B206" s="12" t="inlineStr">
         <is>
-          <t>Solterra (Mesquite — Huffines Communities)</t>
+          <t>Solterra (Mesquite, Huffines Communities)</t>
         </is>
       </c>
       <c r="C206" s="12" t="inlineStr">
@@ -26096,7 +26084,7 @@
       </c>
       <c r="B207" s="6" t="inlineStr">
         <is>
-          <t>Solterra (Mesquite — Huffines Communities)</t>
+          <t>Solterra (Mesquite, Huffines Communities)</t>
         </is>
       </c>
       <c r="C207" s="6" t="inlineStr">
@@ -26221,7 +26209,7 @@
       </c>
       <c r="B208" s="12" t="inlineStr">
         <is>
-          <t>Star Trail (Prosper — Blue Star Land / Jones family)</t>
+          <t>Star Trail (Prosper, Blue Star Land)</t>
         </is>
       </c>
       <c r="C208" s="12" t="inlineStr">
@@ -27104,7 +27092,7 @@
       </c>
       <c r="B215" s="6" t="inlineStr">
         <is>
-          <t>Trinity Falls (Johnson Development — McKinney)</t>
+          <t>Trinity Falls (McKinney, Johnson Development)</t>
         </is>
       </c>
       <c r="C215" s="6" t="inlineStr">
@@ -27721,7 +27709,7 @@
       </c>
       <c r="B220" s="12" t="inlineStr">
         <is>
-          <t>Windsong Ranch (Tellus Group — Prosper)</t>
+          <t>Windsong Ranch (Prosper, Tellus Group)</t>
         </is>
       </c>
       <c r="C220" s="12" t="inlineStr">
@@ -27759,7 +27747,7 @@
       </c>
       <c r="J220" s="15" t="inlineStr">
         <is>
-          <t>A large Prosper masterplan with nine builders on its roster and phases still opening.</t>
+          <t>A Prosper masterplan with nine builders on its roster and phases still opening.</t>
         </is>
       </c>
       <c r="K220" s="14" t="inlineStr">
@@ -27971,773 +27959,15 @@
       <c r="AC221" s="6" t="inlineStr"/>
       <c r="AD221" s="6" t="inlineStr"/>
     </row>
-    <row r="222">
-      <c r="A222" s="12" t="inlineStr">
-        <is>
-          <t>no contact identified</t>
-        </is>
-      </c>
-      <c r="B222" s="12" t="inlineStr">
-        <is>
-          <t>Titan ICF</t>
-        </is>
-      </c>
-      <c r="C222" s="12" t="inlineStr"/>
-      <c r="D222" s="13" t="inlineStr">
-        <is>
-          <t>Held off the deck</t>
-        </is>
-      </c>
-      <c r="E222" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="F222" s="12" t="inlineStr">
-        <is>
-          <t>Builds the wall</t>
-        </is>
-      </c>
-      <c r="G222" s="12" t="inlineStr">
-        <is>
-          <t>Installs across Texas</t>
-        </is>
-      </c>
-      <c r="H222" s="12" t="inlineStr">
-        <is>
-          <t>Texas ICF installer, wall-only or full shell</t>
-        </is>
-      </c>
-      <c r="I222" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J222" s="15" t="inlineStr">
-        <is>
-          <t>The same ICF wall and shell system installed repeatedly on homes and light commercial jobs across Texas.</t>
-        </is>
-      </c>
-      <c r="K222" s="14" t="inlineStr">
-        <is>
-          <t>Partly</t>
-        </is>
-      </c>
-      <c r="L222" s="15" t="inlineStr">
-        <is>
-          <t>No published home count.</t>
-        </is>
-      </c>
-      <c r="M222" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N222" s="15" t="inlineStr">
-        <is>
-          <t>Its core offer is ICF, a concrete wall system it installs as its own method.</t>
-        </is>
-      </c>
-      <c r="O222" s="10" t="inlineStr"/>
-      <c r="P222" s="12" t="inlineStr"/>
-      <c r="Q222" s="16">
-        <f>IF(O222="","ADD LINKEDIN","ok")</f>
-        <v/>
-      </c>
-      <c r="R222" s="12" t="inlineStr">
-        <is>
-          <t>https://titanicf.com/</t>
-        </is>
-      </c>
-      <c r="S222" s="15" t="inlineStr">
-        <is>
-          <t>Already installs concrete walls in ICF, mostly on homes.</t>
-        </is>
-      </c>
-      <c r="T222" s="12" t="inlineStr"/>
-      <c r="U222" s="15" t="inlineStr"/>
-      <c r="V222" s="12" t="inlineStr"/>
-      <c r="W222" s="12" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/titan-icf/</t>
-        </is>
-      </c>
-      <c r="X222" s="12" t="inlineStr">
-        <is>
-          <t>https://titanicf.com/icf-installation-services/</t>
-        </is>
-      </c>
-      <c r="Y222" s="12" t="inlineStr"/>
-      <c r="Z222" s="12" t="inlineStr">
-        <is>
-          <t>(956) 266-7802</t>
-        </is>
-      </c>
-      <c r="AA222" s="12" t="inlineStr">
-        <is>
-          <t>Main line, Rio Grande Valley area code</t>
-        </is>
-      </c>
-      <c r="AB222" s="12" t="inlineStr">
-        <is>
-          <t>https://titanicf.com/</t>
-        </is>
-      </c>
-      <c r="AC222" s="12" t="inlineStr"/>
-      <c r="AD222" s="12" t="inlineStr"/>
-    </row>
     <row r="223">
-      <c r="A223" s="6" t="inlineStr">
-        <is>
-          <t>Don Dykstra</t>
-        </is>
-      </c>
-      <c r="B223" s="6" t="inlineStr">
-        <is>
-          <t>Bloomfield Homes</t>
-        </is>
-      </c>
-      <c r="C223" s="6" t="inlineStr">
-        <is>
-          <t>Co-founder and Chairman</t>
-        </is>
-      </c>
-      <c r="D223" s="7" t="inlineStr">
-        <is>
-          <t>Held off the deck</t>
-        </is>
-      </c>
-      <c r="E223" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F223" s="6" t="inlineStr">
-        <is>
-          <t>Buys walls</t>
-        </is>
-      </c>
-      <c r="G223" s="6" t="inlineStr">
-        <is>
-          <t>Southlake, with communities across Dallas-Fort Worth</t>
-        </is>
-      </c>
-      <c r="H223" s="6" t="inlineStr">
-        <is>
-          <t>2,036 DFW closings in 2024, 4.6% share</t>
-        </is>
-      </c>
-      <c r="I223" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J223" s="9" t="inlineStr">
-        <is>
-          <t>Production plans across DFW communities from a Southlake headquarters that also develops land.</t>
-        </is>
-      </c>
-      <c r="K223" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L223" s="9" t="inlineStr">
-        <is>
-          <t>2,036 DFW closings in 2024 on BUILDER's Local Leaders table, above 1,500.</t>
-        </is>
-      </c>
-      <c r="M223" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N223" s="9" t="inlineStr">
-        <is>
-          <t>Nothing on record. Press coverage covers buyer incentives and community giving.</t>
-        </is>
-      </c>
-      <c r="O223" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/dondykstra</t>
-        </is>
-      </c>
-      <c r="P223" s="6" t="inlineStr"/>
-      <c r="Q223" s="11">
-        <f>IF(O223="","ADD LINKEDIN","ok")</f>
-        <v/>
-      </c>
-      <c r="R223" s="6" t="inlineStr">
-        <is>
-          <t>https://www.bloomfieldhomes.com/</t>
-        </is>
-      </c>
-      <c r="S223" s="9" t="inlineStr">
-        <is>
-          <t>Family-owned, and its about page describes it as a land purchaser and developer.</t>
-        </is>
-      </c>
-      <c r="T223" s="6" t="inlineStr"/>
-      <c r="U223" s="9" t="inlineStr">
-        <is>
-          <t>Indexed title reads Don Dykstra - Chairman - Bloomfield Homes. Named on the Dallas Builders Association's 2025 Hugh Prather Award page as co-founder and chairman.</t>
-        </is>
-      </c>
-      <c r="V223" s="6" t="inlineStr">
-        <is>
-          <t>https://www.dallasbuilders.org/don-dykstra-of-bloomfield-homes-is-2025-hugh-prather-award-honoree/</t>
-        </is>
-      </c>
-      <c r="W223" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/bloomfield-homes/</t>
-        </is>
-      </c>
-      <c r="X223" s="6" t="inlineStr">
-        <is>
-          <t>https://www.bloomfieldhomes.com/about-us/</t>
-        </is>
-      </c>
-      <c r="Y223" s="6" t="inlineStr">
-        <is>
-          <t>2025-09-19 Dallas Builders Association. Don Dykstra of Bloomfield Homes Is 2025 Hugh Prather Award Honoree  https://www.dallasbuilders.org/don-dykstra-of-bloomfield-homes-is-2025-hugh-prather-award-honoree/</t>
-        </is>
-      </c>
-      <c r="Z223" s="6" t="inlineStr">
-        <is>
-          <t>(817) 416-1572</t>
-        </is>
-      </c>
-      <c r="AA223" s="6" t="inlineStr">
-        <is>
-          <t>Corporate office, Southlake</t>
-        </is>
-      </c>
-      <c r="AB223" s="6" t="inlineStr">
-        <is>
-          <t>https://www.bloomfieldhomes.com/about-us/</t>
-        </is>
-      </c>
-      <c r="AC223" s="6" t="inlineStr"/>
-      <c r="AD223" s="6" t="inlineStr"/>
-    </row>
-    <row r="224">
-      <c r="A224" s="12" t="inlineStr">
-        <is>
-          <t>Aaron Graham</t>
-        </is>
-      </c>
-      <c r="B224" s="12" t="inlineStr">
-        <is>
-          <t>Highland Homes</t>
-        </is>
-      </c>
-      <c r="C224" s="12" t="inlineStr">
-        <is>
-          <t>Chairman and Chief Executive Officer</t>
-        </is>
-      </c>
-      <c r="D224" s="13" t="inlineStr">
-        <is>
-          <t>Held off the deck</t>
-        </is>
-      </c>
-      <c r="E224" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F224" s="12" t="inlineStr">
-        <is>
-          <t>Buys walls</t>
-        </is>
-      </c>
-      <c r="G224" s="12" t="inlineStr">
-        <is>
-          <t>Plano, building across Dallas-Fort Worth, Houston, Austin and San Antonio</t>
-        </is>
-      </c>
-      <c r="H224" s="12" t="inlineStr">
-        <is>
-          <t>2,115 DFW closings in 2024, 4.8% share</t>
-        </is>
-      </c>
-      <c r="I224" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J224" s="15" t="inlineStr">
-        <is>
-          <t>Production plans repeated across four Texas metros under one builder.</t>
-        </is>
-      </c>
-      <c r="K224" s="14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L224" s="15" t="inlineStr">
-        <is>
-          <t>2,115 DFW closings in 2024 on BUILDER's 2025 Local Leaders table, above 1,500.</t>
-        </is>
-      </c>
-      <c r="M224" s="14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N224" s="15" t="inlineStr">
-        <is>
-          <t>Nothing on record about wall or structural method.</t>
-        </is>
-      </c>
-      <c r="O224" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/aaron-graham-38728878/</t>
-        </is>
-      </c>
-      <c r="P224" s="12" t="inlineStr"/>
-      <c r="Q224" s="16">
-        <f>IF(O224="","ADD LINKEDIN","ok")</f>
-        <v/>
-      </c>
-      <c r="R224" s="12" t="inlineStr">
-        <is>
-          <t>https://www.highlandhomes.com/</t>
-        </is>
-      </c>
-      <c r="S224" s="15" t="inlineStr">
-        <is>
-          <t>Employee-owned, building in four Texas metros, with a build-to-rent arm, HHS Residential. Supply chain reports to the Chief Operating Officer.</t>
-        </is>
-      </c>
-      <c r="T224" s="12" t="inlineStr"/>
-      <c r="U224" s="15" t="inlineStr">
-        <is>
-          <t>Indexed title reads Aaron Graham - Highland Homes. Named in Builder and Developer, August 6, 2026, as Chairman and CEO of Highland Homes.</t>
-        </is>
-      </c>
-      <c r="V224" s="12" t="inlineStr">
-        <is>
-          <t>https://www.bdmag.com/highland-homes-announces-restructuring/</t>
-        </is>
-      </c>
-      <c r="W224" s="12" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/highland-homes/</t>
-        </is>
-      </c>
-      <c r="X224" s="12" t="inlineStr">
-        <is>
-          <t>https://www.bdmag.com/highland-homes-announces-restructuring/</t>
-        </is>
-      </c>
-      <c r="Y224" s="12" t="inlineStr">
-        <is>
-          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
-        </is>
-      </c>
-      <c r="Z224" s="12" t="inlineStr">
-        <is>
-          <t>(972) 789-3500</t>
-        </is>
-      </c>
-      <c r="AA224" s="12" t="inlineStr">
-        <is>
-          <t>DFW office, Plano</t>
-        </is>
-      </c>
-      <c r="AB224" s="12" t="inlineStr">
-        <is>
-          <t>https://www.highlandhomes.com/contact</t>
-        </is>
-      </c>
-      <c r="AC224" s="12" t="inlineStr"/>
-      <c r="AD224" s="12" t="inlineStr"/>
-    </row>
-    <row r="225">
-      <c r="A225" s="6" t="inlineStr">
-        <is>
-          <t>Stephen Chambers</t>
-        </is>
-      </c>
-      <c r="B225" s="6" t="inlineStr">
-        <is>
-          <t>Highland Homes</t>
-        </is>
-      </c>
-      <c r="C225" s="6" t="inlineStr">
-        <is>
-          <t>Chief Operating Officer</t>
-        </is>
-      </c>
-      <c r="D225" s="7" t="inlineStr">
-        <is>
-          <t>Held off the deck</t>
-        </is>
-      </c>
-      <c r="E225" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F225" s="6" t="inlineStr">
-        <is>
-          <t>Buys walls</t>
-        </is>
-      </c>
-      <c r="G225" s="6" t="inlineStr">
-        <is>
-          <t>Plano, building across Dallas-Fort Worth, Houston, Austin and San Antonio</t>
-        </is>
-      </c>
-      <c r="H225" s="6" t="inlineStr">
-        <is>
-          <t>2,115 DFW closings in 2024, 4.8% share</t>
-        </is>
-      </c>
-      <c r="I225" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J225" s="9" t="inlineStr">
-        <is>
-          <t>Production plans repeated across four Texas metros under one builder.</t>
-        </is>
-      </c>
-      <c r="K225" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L225" s="9" t="inlineStr">
-        <is>
-          <t>2,115 DFW closings in 2024 on BUILDER's 2025 Local Leaders table, above 1,500.</t>
-        </is>
-      </c>
-      <c r="M225" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N225" s="9" t="inlineStr">
-        <is>
-          <t>Nothing on record about wall or structural method.</t>
-        </is>
-      </c>
-      <c r="O225" s="10" t="inlineStr"/>
-      <c r="P225" s="6" t="inlineStr"/>
-      <c r="Q225" s="11">
-        <f>IF(O225="","ADD LINKEDIN","ok")</f>
-        <v/>
-      </c>
-      <c r="R225" s="6" t="inlineStr">
-        <is>
-          <t>https://www.highlandhomes.com/</t>
-        </is>
-      </c>
-      <c r="S225" s="9" t="inlineStr">
-        <is>
-          <t>Employee-owned, building in four Texas metros, with a build-to-rent arm, HHS Residential. Supply chain reports to the Chief Operating Officer.</t>
-        </is>
-      </c>
-      <c r="T225" s="6" t="inlineStr"/>
-      <c r="U225" s="9" t="inlineStr">
-        <is>
-          <t>Named in the same Builder and Developer article as promoted to Chief Operating Officer, over architectural services, new product development, supply chain, IT and marketing.</t>
-        </is>
-      </c>
-      <c r="V225" s="6" t="inlineStr">
-        <is>
-          <t>https://www.bdmag.com/highland-homes-announces-restructuring/</t>
-        </is>
-      </c>
-      <c r="W225" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/highland-homes/</t>
-        </is>
-      </c>
-      <c r="X225" s="6" t="inlineStr">
-        <is>
-          <t>https://www.bdmag.com/highland-homes-announces-restructuring/</t>
-        </is>
-      </c>
-      <c r="Y225" s="6" t="inlineStr">
-        <is>
-          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
-        </is>
-      </c>
-      <c r="Z225" s="6" t="inlineStr">
-        <is>
-          <t>(972) 789-3500</t>
-        </is>
-      </c>
-      <c r="AA225" s="6" t="inlineStr">
-        <is>
-          <t>DFW office, Plano</t>
-        </is>
-      </c>
-      <c r="AB225" s="6" t="inlineStr">
-        <is>
-          <t>https://www.highlandhomes.com/contact</t>
-        </is>
-      </c>
-      <c r="AC225" s="6" t="inlineStr"/>
-      <c r="AD225" s="6" t="inlineStr"/>
-    </row>
-    <row r="226">
-      <c r="A226" s="12" t="inlineStr">
-        <is>
-          <t>Amy Jones</t>
-        </is>
-      </c>
-      <c r="B226" s="12" t="inlineStr">
-        <is>
-          <t>Highland Homes</t>
-        </is>
-      </c>
-      <c r="C226" s="12" t="inlineStr">
-        <is>
-          <t>Senior Vice President of Sales and Marketing, Dallas-Fort Worth</t>
-        </is>
-      </c>
-      <c r="D226" s="13" t="inlineStr">
-        <is>
-          <t>Held off the deck</t>
-        </is>
-      </c>
-      <c r="E226" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F226" s="12" t="inlineStr">
-        <is>
-          <t>Buys walls</t>
-        </is>
-      </c>
-      <c r="G226" s="12" t="inlineStr">
-        <is>
-          <t>Plano, building across Dallas-Fort Worth, Houston, Austin and San Antonio</t>
-        </is>
-      </c>
-      <c r="H226" s="12" t="inlineStr">
-        <is>
-          <t>2,115 DFW closings in 2024, 4.8% share</t>
-        </is>
-      </c>
-      <c r="I226" s="14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J226" s="15" t="inlineStr">
-        <is>
-          <t>Production plans repeated across four Texas metros under one builder.</t>
-        </is>
-      </c>
-      <c r="K226" s="14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L226" s="15" t="inlineStr">
-        <is>
-          <t>2,115 DFW closings in 2024 on BUILDER's 2025 Local Leaders table, above 1,500.</t>
-        </is>
-      </c>
-      <c r="M226" s="14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N226" s="15" t="inlineStr">
-        <is>
-          <t>Nothing on record about wall or structural method.</t>
-        </is>
-      </c>
-      <c r="O226" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/amy-jones-ba6324191</t>
-        </is>
-      </c>
-      <c r="P226" s="12" t="inlineStr"/>
-      <c r="Q226" s="16">
-        <f>IF(O226="","ADD LINKEDIN","ok")</f>
-        <v/>
-      </c>
-      <c r="R226" s="12" t="inlineStr">
-        <is>
-          <t>https://www.highlandhomes.com/</t>
-        </is>
-      </c>
-      <c r="S226" s="15" t="inlineStr">
-        <is>
-          <t>Employee-owned, building in four Texas metros, with a build-to-rent arm, HHS Residential. Supply chain reports to the Chief Operating Officer.</t>
-        </is>
-      </c>
-      <c r="T226" s="12" t="inlineStr"/>
-      <c r="U226" s="15" t="inlineStr">
-        <is>
-          <t>Indexed title reads Amy Jones - Senior Vice President of Sales at Highland Homes. Named in the same article as promoted to Senior Vice President of Sales and Marketing in Dallas-Fort Worth.</t>
-        </is>
-      </c>
-      <c r="V226" s="12" t="inlineStr">
-        <is>
-          <t>https://www.bdmag.com/highland-homes-announces-restructuring/</t>
-        </is>
-      </c>
-      <c r="W226" s="12" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/highland-homes/</t>
-        </is>
-      </c>
-      <c r="X226" s="12" t="inlineStr">
-        <is>
-          <t>https://www.bdmag.com/highland-homes-announces-restructuring/</t>
-        </is>
-      </c>
-      <c r="Y226" s="12" t="inlineStr">
-        <is>
-          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
-        </is>
-      </c>
-      <c r="Z226" s="12" t="inlineStr">
-        <is>
-          <t>(972) 789-3500</t>
-        </is>
-      </c>
-      <c r="AA226" s="12" t="inlineStr">
-        <is>
-          <t>DFW office, Plano</t>
-        </is>
-      </c>
-      <c r="AB226" s="12" t="inlineStr">
-        <is>
-          <t>https://www.highlandhomes.com/contact</t>
-        </is>
-      </c>
-      <c r="AC226" s="12" t="inlineStr"/>
-      <c r="AD226" s="12" t="inlineStr"/>
-    </row>
-    <row r="227">
-      <c r="A227" s="6" t="inlineStr">
-        <is>
-          <t>John Winniford</t>
-        </is>
-      </c>
-      <c r="B227" s="6" t="inlineStr">
-        <is>
-          <t>Brightland Homes</t>
-        </is>
-      </c>
-      <c r="C227" s="6" t="inlineStr">
-        <is>
-          <t>Former President and CEO</t>
-        </is>
-      </c>
-      <c r="D227" s="7" t="inlineStr">
-        <is>
-          <t>Held off the deck</t>
-        </is>
-      </c>
-      <c r="E227" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F227" s="6" t="inlineStr">
-        <is>
-          <t>Buys walls</t>
-        </is>
-      </c>
-      <c r="G227" s="6" t="inlineStr">
-        <is>
-          <t>Addison origin, building in DFW and other states</t>
-        </is>
-      </c>
-      <c r="H227" s="6" t="inlineStr">
-        <is>
-          <t>3,162 closings company-wide in 2024, per BUILDER</t>
-        </is>
-      </c>
-      <c r="I227" s="8" t="inlineStr">
-        <is>
-          <t>Partly</t>
-        </is>
-      </c>
-      <c r="J227" s="9" t="inlineStr">
-        <is>
-          <t>Production plans historically across DFW, on a multi-state platform that spreads repetition across metros.</t>
-        </is>
-      </c>
-      <c r="K227" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L227" s="9" t="inlineStr">
-        <is>
-          <t>3,162 closings company-wide in 2024 is above 1,500, and since April 1, 2025 the firm sits inside DRB Group.</t>
-        </is>
-      </c>
-      <c r="M227" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N227" s="9" t="inlineStr">
-        <is>
-          <t>Nothing on record about construction method. The 2023 rebrand was a change of name.</t>
-        </is>
-      </c>
-      <c r="O227" s="10" t="inlineStr"/>
-      <c r="P227" s="6" t="inlineStr"/>
-      <c r="Q227" s="11">
-        <f>IF(O227="","ADD LINKEDIN","ok")</f>
-        <v/>
-      </c>
-      <c r="R227" s="6" t="inlineStr">
-        <is>
-          <t>https://www.brightlandhomes.com/</t>
-        </is>
-      </c>
-      <c r="S227" s="9" t="inlineStr">
-        <is>
-          <t>Folded into DRB Group on April 1, 2025. Both are subsidiaries of Sumitomo Forestry America.</t>
-        </is>
-      </c>
-      <c r="T227" s="6" t="inlineStr"/>
-      <c r="U227" s="9" t="inlineStr">
-        <is>
-          <t>Named President and CEO in the firm's February 21, 2023 rebrand release.</t>
-        </is>
-      </c>
-      <c r="V227" s="6" t="inlineStr">
-        <is>
-          <t>https://press.brightlandhomes.com/gehan-homes-announces-name-change-to-brightland-homes</t>
-        </is>
-      </c>
-      <c r="W227" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/brightlandhomes/</t>
-        </is>
-      </c>
-      <c r="X227" s="6" t="inlineStr">
-        <is>
-          <t>https://press.brightlandhomes.com/gehan-homes-announces-name-change-to-brightland-homes</t>
-        </is>
-      </c>
-      <c r="Y227" s="6" t="inlineStr">
-        <is>
-          <t>2023 Dallas Innovates. Addison’s Gehan Homes Rebrands Its Business as Brightland Homes  https://dallasinnovates.com/addisons-gehan-homes-rebrands-its-business-as-brightland-homes/</t>
-        </is>
-      </c>
-      <c r="Z227" s="6" t="inlineStr"/>
-      <c r="AA227" s="6" t="inlineStr"/>
-      <c r="AB227" s="6" t="inlineStr"/>
-      <c r="AC227" s="6" t="inlineStr"/>
-      <c r="AD227" s="6" t="inlineStr"/>
-    </row>
-    <row r="229">
-      <c r="A229" s="17" t="inlineStr">
+      <c r="A223" s="17" t="inlineStr">
         <is>
           <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; the verification column records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. The Find column searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Rolodex, Dallas-Fort Worth, 2026-09-24.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:AD227"/>
+  <autoFilter ref="A6:AD221"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -28781,7 +28011,7 @@
     <row r="2">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Source: HUD SOCDS, republishing the Census Building Permits Survey. An authorisation is not a start, a completion or a closing. Census counts townhouses and row houses as single family. The jurisdictions sum to the counties and the counties sum to the metro exactly, in every year.</t>
+          <t>Source: Census Building Permits Survey, annual county files. An authorisation is not a start, a completion or a closing. Census counts townhouses and row houses as single family. The counties sum to the metro. The jurisdictions are the largest 50 and do not sum to the counties.</t>
         </is>
       </c>
     </row>

--- a/docs/DFW_Rolodex.xlsx
+++ b/docs/DFW_Rolodex.xlsx
@@ -10940,7 +10940,7 @@
       </c>
       <c r="H87" s="6" t="inlineStr">
         <is>
-          <t>Trussway had six plants and 1,000 staff when bought, 2022</t>
+          <t>Fort Worth truss and wall-panel plant, formerly Trussway</t>
         </is>
       </c>
       <c r="I87" s="8" t="inlineStr">
@@ -11053,7 +11053,7 @@
       </c>
       <c r="H88" s="12" t="inlineStr">
         <is>
-          <t>Serving the Texas market since 1988</t>
+          <t>Cedar Park precast plant, named North Texas consultant</t>
         </is>
       </c>
       <c r="I88" s="14" t="inlineStr">
@@ -11174,7 +11174,7 @@
       </c>
       <c r="H89" s="6" t="inlineStr">
         <is>
-          <t>Serving the Texas market since 1988</t>
+          <t>Cedar Park precast plant, named North Texas consultant</t>
         </is>
       </c>
       <c r="I89" s="8" t="inlineStr">

--- a/docs/DFW_Rolodex.xlsx
+++ b/docs/DFW_Rolodex.xlsx
@@ -5268,11 +5268,7 @@
         </is>
       </c>
       <c r="X41" s="6" t="inlineStr"/>
-      <c r="Y41" s="6" t="inlineStr">
-        <is>
-          <t>2023-07-07 Dallas Morning News. Chicago builder that left D-FW returns to area, takes 1,500 home sites  https://www.dallasnews.com/business/real-estate/2023/07/07/chicago-builder-that-left-d-fw-returns-to-area-takes-1500-home-sites/</t>
-        </is>
-      </c>
+      <c r="Y41" s="6" t="inlineStr"/>
       <c r="Z41" s="6" t="inlineStr"/>
       <c r="AA41" s="6" t="inlineStr"/>
       <c r="AB41" s="6" t="inlineStr"/>
@@ -6397,11 +6393,7 @@
           <t>https://www.firsttexashomes.com/about/</t>
         </is>
       </c>
-      <c r="Y50" s="12" t="inlineStr">
-        <is>
-          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
-        </is>
-      </c>
+      <c r="Y50" s="12" t="inlineStr"/>
       <c r="Z50" s="12" t="inlineStr">
         <is>
           <t>(214) 613-3400</t>
@@ -18109,7 +18101,7 @@
       </c>
       <c r="Y144" s="12" t="inlineStr">
         <is>
-          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
+          <t>2024-03-11 PR Newswire / Apis Cor. Apis Cor announces strategic investment by D.R. Horton  https://www.prnewswire.com/news-releases/apis-cor-a-manufacturer-of-construction-3d-printing-robots-announces-strategic-investment-by-dr-horton-302084850.html</t>
         </is>
       </c>
       <c r="Z144" s="12" t="inlineStr">
@@ -18238,7 +18230,7 @@
       </c>
       <c r="Y145" s="6" t="inlineStr">
         <is>
-          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
+          <t>2024-03-11 PR Newswire / Apis Cor. Apis Cor announces strategic investment by D.R. Horton  https://www.prnewswire.com/news-releases/apis-cor-a-manufacturer-of-construction-3d-printing-robots-announces-strategic-investment-by-dr-horton-302084850.html</t>
         </is>
       </c>
       <c r="Z145" s="6" t="inlineStr">
@@ -18367,7 +18359,7 @@
       </c>
       <c r="Y146" s="12" t="inlineStr">
         <is>
-          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
+          <t>2024-03-11 PR Newswire / Apis Cor. Apis Cor announces strategic investment by D.R. Horton  https://www.prnewswire.com/news-releases/apis-cor-a-manufacturer-of-construction-3d-printing-robots-announces-strategic-investment-by-dr-horton-302084850.html</t>
         </is>
       </c>
       <c r="Z146" s="12" t="inlineStr">
@@ -18496,7 +18488,7 @@
       </c>
       <c r="Y147" s="6" t="inlineStr">
         <is>
-          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
+          <t>2024-03-11 PR Newswire / Apis Cor. Apis Cor announces strategic investment by D.R. Horton  https://www.prnewswire.com/news-releases/apis-cor-a-manufacturer-of-construction-3d-printing-robots-announces-strategic-investment-by-dr-horton-302084850.html</t>
         </is>
       </c>
       <c r="Z147" s="6" t="inlineStr">
@@ -18631,11 +18623,7 @@
           <t>https://www.businesswire.com/news/home/20250821913928/en/PulteGroup-Promotes-Scott-Bryson-to-Dallas-Division-President</t>
         </is>
       </c>
-      <c r="Y148" s="12" t="inlineStr">
-        <is>
-          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
-        </is>
-      </c>
+      <c r="Y148" s="12" t="inlineStr"/>
       <c r="Z148" s="12" t="inlineStr">
         <is>
           <t>(972) 200-3727</t>
@@ -18764,11 +18752,7 @@
           <t>https://www.davidweekleyhomes.com/about-us</t>
         </is>
       </c>
-      <c r="Y149" s="6" t="inlineStr">
-        <is>
-          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
-        </is>
-      </c>
+      <c r="Y149" s="6" t="inlineStr"/>
       <c r="Z149" s="6" t="inlineStr">
         <is>
           <t>(877) 933-5539</t>
@@ -18893,11 +18877,7 @@
           <t>https://www.davidweekleyhomes.com/about-us</t>
         </is>
       </c>
-      <c r="Y150" s="12" t="inlineStr">
-        <is>
-          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
-        </is>
-      </c>
+      <c r="Y150" s="12" t="inlineStr"/>
       <c r="Z150" s="12" t="inlineStr">
         <is>
           <t>(877) 933-5539</t>
@@ -19026,11 +19006,7 @@
           <t>https://www.davidweekleyhomes.com/about-us</t>
         </is>
       </c>
-      <c r="Y151" s="6" t="inlineStr">
-        <is>
-          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
-        </is>
-      </c>
+      <c r="Y151" s="6" t="inlineStr"/>
       <c r="Z151" s="6" t="inlineStr">
         <is>
           <t>(877) 933-5539</t>
@@ -19155,11 +19131,7 @@
           <t>https://www.davidweekleyhomes.com/about-us</t>
         </is>
       </c>
-      <c r="Y152" s="12" t="inlineStr">
-        <is>
-          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
-        </is>
-      </c>
+      <c r="Y152" s="12" t="inlineStr"/>
       <c r="Z152" s="12" t="inlineStr">
         <is>
           <t>(877) 933-5539</t>
@@ -19800,11 +19772,7 @@
           <t>https://investors.meritagehomes.com/company-information/management-team</t>
         </is>
       </c>
-      <c r="Y157" s="6" t="inlineStr">
-        <is>
-          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
-        </is>
-      </c>
+      <c r="Y157" s="6" t="inlineStr"/>
       <c r="Z157" s="6" t="inlineStr">
         <is>
           <t>(469) 487-7973</t>
@@ -19933,11 +19901,7 @@
           <t>https://investors.meritagehomes.com/company-information/management-team</t>
         </is>
       </c>
-      <c r="Y158" s="12" t="inlineStr">
-        <is>
-          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
-        </is>
-      </c>
+      <c r="Y158" s="12" t="inlineStr"/>
       <c r="Z158" s="12" t="inlineStr">
         <is>
           <t>(469) 487-7973</t>
@@ -20066,11 +20030,7 @@
           <t>https://investors.meritagehomes.com/company-information/management-team</t>
         </is>
       </c>
-      <c r="Y159" s="6" t="inlineStr">
-        <is>
-          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
-        </is>
-      </c>
+      <c r="Y159" s="6" t="inlineStr"/>
       <c r="Z159" s="6" t="inlineStr">
         <is>
           <t>(469) 487-7973</t>
@@ -20199,11 +20159,7 @@
           <t>https://www.ashtonwoods.com/corporate-info</t>
         </is>
       </c>
-      <c r="Y160" s="12" t="inlineStr">
-        <is>
-          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
-        </is>
-      </c>
+      <c r="Y160" s="12" t="inlineStr"/>
       <c r="Z160" s="12" t="inlineStr">
         <is>
           <t>(770) 998-9663</t>
@@ -20336,11 +20292,7 @@
           <t>https://www.ashtonwoods.com/corporate-info</t>
         </is>
       </c>
-      <c r="Y161" s="6" t="inlineStr">
-        <is>
-          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
-        </is>
-      </c>
+      <c r="Y161" s="6" t="inlineStr"/>
       <c r="Z161" s="6" t="inlineStr">
         <is>
           <t>(770) 998-9663</t>
@@ -20473,11 +20425,7 @@
           <t>https://www.ashtonwoods.com/corporate-info</t>
         </is>
       </c>
-      <c r="Y162" s="12" t="inlineStr">
-        <is>
-          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
-        </is>
-      </c>
+      <c r="Y162" s="12" t="inlineStr"/>
       <c r="Z162" s="12" t="inlineStr">
         <is>
           <t>(770) 998-9663</t>
@@ -20606,11 +20554,7 @@
           <t>https://www.ashtonwoods.com/corporate-info</t>
         </is>
       </c>
-      <c r="Y163" s="6" t="inlineStr">
-        <is>
-          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
-        </is>
-      </c>
+      <c r="Y163" s="6" t="inlineStr"/>
       <c r="Z163" s="6" t="inlineStr">
         <is>
           <t>(770) 998-9663</t>
@@ -20735,11 +20679,7 @@
           <t>https://www.perryhomes.com/about-perry-homes</t>
         </is>
       </c>
-      <c r="Y164" s="12" t="inlineStr">
-        <is>
-          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
-        </is>
-      </c>
+      <c r="Y164" s="12" t="inlineStr"/>
       <c r="Z164" s="12" t="inlineStr">
         <is>
           <t>(800) 247-3779</t>
@@ -20868,11 +20808,7 @@
           <t>https://www.perryhomes.com/about-perry-homes</t>
         </is>
       </c>
-      <c r="Y165" s="6" t="inlineStr">
-        <is>
-          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
-        </is>
-      </c>
+      <c r="Y165" s="6" t="inlineStr"/>
       <c r="Z165" s="6" t="inlineStr">
         <is>
           <t>(800) 247-3779</t>
@@ -21384,11 +21320,7 @@
           <t>https://greenbrickpartners.com/leadership/</t>
         </is>
       </c>
-      <c r="Y169" s="6" t="inlineStr">
-        <is>
-          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
-        </is>
-      </c>
+      <c r="Y169" s="6" t="inlineStr"/>
       <c r="Z169" s="6" t="inlineStr">
         <is>
           <t>(469) 573-6721</t>
@@ -21517,11 +21449,7 @@
           <t>https://greenbrickpartners.com/leadership/</t>
         </is>
       </c>
-      <c r="Y170" s="12" t="inlineStr">
-        <is>
-          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
-        </is>
-      </c>
+      <c r="Y170" s="12" t="inlineStr"/>
       <c r="Z170" s="12" t="inlineStr">
         <is>
           <t>(469) 573-6721</t>
@@ -21646,11 +21574,7 @@
           <t>https://greenbrickpartners.com/leadership/</t>
         </is>
       </c>
-      <c r="Y171" s="6" t="inlineStr">
-        <is>
-          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
-        </is>
-      </c>
+      <c r="Y171" s="6" t="inlineStr"/>
       <c r="Z171" s="6" t="inlineStr">
         <is>
           <t>(469) 573-6721</t>
@@ -21779,11 +21703,7 @@
           <t>https://greenbrickpartners.com/leadership/</t>
         </is>
       </c>
-      <c r="Y172" s="12" t="inlineStr">
-        <is>
-          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
-        </is>
-      </c>
+      <c r="Y172" s="12" t="inlineStr"/>
       <c r="Z172" s="12" t="inlineStr">
         <is>
           <t>(469) 573-6721</t>
@@ -27892,11 +27812,7 @@
           <t>https://www.lennar.com/about/leadership/david-grove</t>
         </is>
       </c>
-      <c r="Y221" s="6" t="inlineStr">
-        <is>
-          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
-        </is>
-      </c>
+      <c r="Y221" s="6" t="inlineStr"/>
       <c r="Z221" s="6" t="inlineStr">
         <is>
           <t>(866) 314-4477</t>

--- a/docs/DFW_Rolodex.xlsx
+++ b/docs/DFW_Rolodex.xlsx
@@ -5268,7 +5268,11 @@
         </is>
       </c>
       <c r="X41" s="6" t="inlineStr"/>
-      <c r="Y41" s="6" t="inlineStr"/>
+      <c r="Y41" s="6" t="inlineStr">
+        <is>
+          <t>2023-07-07 Dallas Morning News. Chicago builder that left D-FW returns to area, takes 1,500 home sites  https://www.dallasnews.com/business/real-estate/2023/07/07/chicago-builder-that-left-d-fw-returns-to-area-takes-1500-home-sites/</t>
+        </is>
+      </c>
       <c r="Z41" s="6" t="inlineStr"/>
       <c r="AA41" s="6" t="inlineStr"/>
       <c r="AB41" s="6" t="inlineStr"/>
@@ -6393,7 +6397,11 @@
           <t>https://www.firsttexashomes.com/about/</t>
         </is>
       </c>
-      <c r="Y50" s="12" t="inlineStr"/>
+      <c r="Y50" s="12" t="inlineStr">
+        <is>
+          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
+        </is>
+      </c>
       <c r="Z50" s="12" t="inlineStr">
         <is>
           <t>(214) 613-3400</t>
@@ -18623,7 +18631,11 @@
           <t>https://www.businesswire.com/news/home/20250821913928/en/PulteGroup-Promotes-Scott-Bryson-to-Dallas-Division-President</t>
         </is>
       </c>
-      <c r="Y148" s="12" t="inlineStr"/>
+      <c r="Y148" s="12" t="inlineStr">
+        <is>
+          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
+        </is>
+      </c>
       <c r="Z148" s="12" t="inlineStr">
         <is>
           <t>(972) 200-3727</t>
@@ -18752,7 +18764,11 @@
           <t>https://www.davidweekleyhomes.com/about-us</t>
         </is>
       </c>
-      <c r="Y149" s="6" t="inlineStr"/>
+      <c r="Y149" s="6" t="inlineStr">
+        <is>
+          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
+        </is>
+      </c>
       <c r="Z149" s="6" t="inlineStr">
         <is>
           <t>(877) 933-5539</t>
@@ -18877,7 +18893,11 @@
           <t>https://www.davidweekleyhomes.com/about-us</t>
         </is>
       </c>
-      <c r="Y150" s="12" t="inlineStr"/>
+      <c r="Y150" s="12" t="inlineStr">
+        <is>
+          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
+        </is>
+      </c>
       <c r="Z150" s="12" t="inlineStr">
         <is>
           <t>(877) 933-5539</t>
@@ -19006,7 +19026,11 @@
           <t>https://www.davidweekleyhomes.com/about-us</t>
         </is>
       </c>
-      <c r="Y151" s="6" t="inlineStr"/>
+      <c r="Y151" s="6" t="inlineStr">
+        <is>
+          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
+        </is>
+      </c>
       <c r="Z151" s="6" t="inlineStr">
         <is>
           <t>(877) 933-5539</t>
@@ -19131,7 +19155,11 @@
           <t>https://www.davidweekleyhomes.com/about-us</t>
         </is>
       </c>
-      <c r="Y152" s="12" t="inlineStr"/>
+      <c r="Y152" s="12" t="inlineStr">
+        <is>
+          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
+        </is>
+      </c>
       <c r="Z152" s="12" t="inlineStr">
         <is>
           <t>(877) 933-5539</t>
@@ -19772,7 +19800,11 @@
           <t>https://investors.meritagehomes.com/company-information/management-team</t>
         </is>
       </c>
-      <c r="Y157" s="6" t="inlineStr"/>
+      <c r="Y157" s="6" t="inlineStr">
+        <is>
+          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
+        </is>
+      </c>
       <c r="Z157" s="6" t="inlineStr">
         <is>
           <t>(469) 487-7973</t>
@@ -19901,7 +19933,11 @@
           <t>https://investors.meritagehomes.com/company-information/management-team</t>
         </is>
       </c>
-      <c r="Y158" s="12" t="inlineStr"/>
+      <c r="Y158" s="12" t="inlineStr">
+        <is>
+          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
+        </is>
+      </c>
       <c r="Z158" s="12" t="inlineStr">
         <is>
           <t>(469) 487-7973</t>
@@ -20030,7 +20066,11 @@
           <t>https://investors.meritagehomes.com/company-information/management-team</t>
         </is>
       </c>
-      <c r="Y159" s="6" t="inlineStr"/>
+      <c r="Y159" s="6" t="inlineStr">
+        <is>
+          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
+        </is>
+      </c>
       <c r="Z159" s="6" t="inlineStr">
         <is>
           <t>(469) 487-7973</t>
@@ -20159,7 +20199,11 @@
           <t>https://www.ashtonwoods.com/corporate-info</t>
         </is>
       </c>
-      <c r="Y160" s="12" t="inlineStr"/>
+      <c r="Y160" s="12" t="inlineStr">
+        <is>
+          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
+        </is>
+      </c>
       <c r="Z160" s="12" t="inlineStr">
         <is>
           <t>(770) 998-9663</t>
@@ -20292,7 +20336,11 @@
           <t>https://www.ashtonwoods.com/corporate-info</t>
         </is>
       </c>
-      <c r="Y161" s="6" t="inlineStr"/>
+      <c r="Y161" s="6" t="inlineStr">
+        <is>
+          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
+        </is>
+      </c>
       <c r="Z161" s="6" t="inlineStr">
         <is>
           <t>(770) 998-9663</t>
@@ -20425,7 +20473,11 @@
           <t>https://www.ashtonwoods.com/corporate-info</t>
         </is>
       </c>
-      <c r="Y162" s="12" t="inlineStr"/>
+      <c r="Y162" s="12" t="inlineStr">
+        <is>
+          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
+        </is>
+      </c>
       <c r="Z162" s="12" t="inlineStr">
         <is>
           <t>(770) 998-9663</t>
@@ -20554,7 +20606,11 @@
           <t>https://www.ashtonwoods.com/corporate-info</t>
         </is>
       </c>
-      <c r="Y163" s="6" t="inlineStr"/>
+      <c r="Y163" s="6" t="inlineStr">
+        <is>
+          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
+        </is>
+      </c>
       <c r="Z163" s="6" t="inlineStr">
         <is>
           <t>(770) 998-9663</t>
@@ -20679,7 +20735,11 @@
           <t>https://www.perryhomes.com/about-perry-homes</t>
         </is>
       </c>
-      <c r="Y164" s="12" t="inlineStr"/>
+      <c r="Y164" s="12" t="inlineStr">
+        <is>
+          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
+        </is>
+      </c>
       <c r="Z164" s="12" t="inlineStr">
         <is>
           <t>(800) 247-3779</t>
@@ -20808,7 +20868,11 @@
           <t>https://www.perryhomes.com/about-perry-homes</t>
         </is>
       </c>
-      <c r="Y165" s="6" t="inlineStr"/>
+      <c r="Y165" s="6" t="inlineStr">
+        <is>
+          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
+        </is>
+      </c>
       <c r="Z165" s="6" t="inlineStr">
         <is>
           <t>(800) 247-3779</t>
@@ -21320,7 +21384,11 @@
           <t>https://greenbrickpartners.com/leadership/</t>
         </is>
       </c>
-      <c r="Y169" s="6" t="inlineStr"/>
+      <c r="Y169" s="6" t="inlineStr">
+        <is>
+          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
+        </is>
+      </c>
       <c r="Z169" s="6" t="inlineStr">
         <is>
           <t>(469) 573-6721</t>
@@ -21449,7 +21517,11 @@
           <t>https://greenbrickpartners.com/leadership/</t>
         </is>
       </c>
-      <c r="Y170" s="12" t="inlineStr"/>
+      <c r="Y170" s="12" t="inlineStr">
+        <is>
+          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
+        </is>
+      </c>
       <c r="Z170" s="12" t="inlineStr">
         <is>
           <t>(469) 573-6721</t>
@@ -21574,7 +21646,11 @@
           <t>https://greenbrickpartners.com/leadership/</t>
         </is>
       </c>
-      <c r="Y171" s="6" t="inlineStr"/>
+      <c r="Y171" s="6" t="inlineStr">
+        <is>
+          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
+        </is>
+      </c>
       <c r="Z171" s="6" t="inlineStr">
         <is>
           <t>(469) 573-6721</t>
@@ -21703,7 +21779,11 @@
           <t>https://greenbrickpartners.com/leadership/</t>
         </is>
       </c>
-      <c r="Y172" s="12" t="inlineStr"/>
+      <c r="Y172" s="12" t="inlineStr">
+        <is>
+          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
+        </is>
+      </c>
       <c r="Z172" s="12" t="inlineStr">
         <is>
           <t>(469) 573-6721</t>
@@ -27812,7 +27892,11 @@
           <t>https://www.lennar.com/about/leadership/david-grove</t>
         </is>
       </c>
-      <c r="Y221" s="6" t="inlineStr"/>
+      <c r="Y221" s="6" t="inlineStr">
+        <is>
+          <t>2025-07-24 Dallas Morning News. The 10 biggest homebuilders in D-FW  https://www.dallasnews.com/business/real-estate/2025/07/24/list-who-are-the-10-biggest-homebuilders-in-d-fw/</t>
+        </is>
+      </c>
       <c r="Z221" s="6" t="inlineStr">
         <is>
           <t>(866) 314-4477</t>

--- a/docs/DFW_Rolodex.xlsx
+++ b/docs/DFW_Rolodex.xlsx
@@ -586,7 +586,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Héctor Ibarzábal · 2026-09-24</t>
+          <t>Héctor Ibarzábal · 2026-09-26</t>
         </is>
       </c>
     </row>
@@ -27535,7 +27535,7 @@
     <row r="220">
       <c r="A220" s="17" t="inlineStr">
         <is>
-          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; the verification column records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. The Find column searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Rolodex, Dallas-Fort Worth, 2026-09-24.</t>
+          <t>NOTE. A filled LinkedIn cell means the profile was opened or the search result read and the headline named the firm; the verification column records what was read. Where that test failed the cell is left empty rather than guessed, because a fabricated slug passes visual inspection and then fails in front of the person it names. The Find column searches for the empty ones in your own session. Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Rolodex, Dallas-Fort Worth, 2026-09-26.</t>
         </is>
       </c>
     </row>
